--- a/output/pdf_financials_xlsx/RGN.xlsx
+++ b/output/pdf_financials_xlsx/RGN.xlsx
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.001062</v>
+        <v>0.002795</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.00229</v>
+        <v>0.002305</v>
       </c>
     </row>
     <row r="8">
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.084984</v>
       </c>
     </row>
     <row r="65">
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.055816</v>
       </c>
     </row>
     <row r="68">
@@ -3851,7 +3851,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
